--- a/erp-server/erp-server-oms/src/main/resources/excel/fullyManagedOrderTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/fullyManagedOrderTemplate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -46,6 +53,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -60,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -74,6 +95,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -88,6 +116,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -102,6 +137,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -116,6 +158,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -130,6 +179,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -162,6 +218,81 @@
   </si>
   <si>
     <t>要求发货时间</t>
+  </si>
+  <si>
+    <t>要求收货时间</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SKU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>下单数量</t>
+    </r>
+  </si>
+  <si>
+    <t>发货仓库</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>真实售价</t>
+    </r>
+  </si>
+  <si>
+    <t>税率%</t>
   </si>
   <si>
     <t>CZK</t>
@@ -897,7 +1028,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -924,6 +1055,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1273,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" customWidth="1"/>
@@ -1289,10 +1423,10 @@
     <col min="12" max="12" width="11.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="17.875" style="2" customWidth="1"/>
     <col min="14" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="15" max="16" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:15">
+    <row r="1" ht="35.25" customHeight="1" spans="1:21">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1337,6 +1471,24 @@
       </c>
       <c r="O1" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:3">
@@ -1364,177 +1516,177 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/fullyManagedOrderTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/fullyManagedOrderTemplate.xlsx
@@ -179,13 +179,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -195,7 +188,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>平台来源</t>
+      <t>订单来源</t>
     </r>
   </si>
   <si>

--- a/erp-server/erp-server-oms/src/main/resources/excel/fullyManagedOrderTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/fullyManagedOrderTemplate.xlsx
@@ -179,6 +179,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -285,7 +292,19 @@
     </r>
   </si>
   <si>
-    <t>税率%</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>税率%</t>
+    </r>
   </si>
   <si>
     <t>CZK</t>
@@ -1480,7 +1499,7 @@
       <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="9" t="s">
         <v>20</v>
       </c>
     </row>
